--- a/products/store_b/out/09_Freelancer_Income_Quarterly_Tax_Tracker.xlsx
+++ b/products/store_b/out/09_Freelancer_Income_Quarterly_Tax_Tracker.xlsx
@@ -1178,11 +1178,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="42218061"/>
-        <c:axId val="46417100"/>
+        <c:axId val="58164798"/>
+        <c:axId val="65058215"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="42218061"/>
+        <c:axId val="58164798"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1214,7 +1214,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46417100"/>
+        <c:crossAx val="65058215"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1222,7 +1222,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="46417100"/>
+        <c:axId val="65058215"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1264,7 +1264,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42218061"/>
+        <c:crossAx val="58164798"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1456,11 +1456,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="87583018"/>
-        <c:axId val="89499342"/>
+        <c:axId val="15630806"/>
+        <c:axId val="3825702"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="87583018"/>
+        <c:axId val="15630806"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1492,7 +1492,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89499342"/>
+        <c:crossAx val="3825702"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1500,7 +1500,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="89499342"/>
+        <c:axId val="3825702"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1542,7 +1542,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87583018"/>
+        <c:crossAx val="15630806"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
